--- a/data/trans_bre/P57GLOBAL_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 7,79</t>
+          <t>-4,58; 8,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 11,13</t>
+          <t>-1,9; 11,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 7,34</t>
+          <t>-3,86; 7,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 13,79</t>
+          <t>-8,19; 14,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 13,66</t>
+          <t>-7,11; 13,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 19,76</t>
+          <t>-2,92; 20,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 9,87</t>
+          <t>-4,61; 9,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 34,62</t>
+          <t>-15,75; 38,92</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 6,33</t>
+          <t>-3,65; 6,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,58</t>
+          <t>2,3; 12,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,12</t>
+          <t>-4,93; 4,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -4,48</t>
+          <t>-33,25; -4,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 9,77</t>
+          <t>-5,16; 9,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 19,72</t>
+          <t>3,4; 20,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 5,15</t>
+          <t>-5,86; 5,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,54; -7,87</t>
+          <t>-52,2; -7,84</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 5,43</t>
+          <t>-4,05; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 9,25</t>
+          <t>-0,87; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,5</t>
+          <t>-3,93; 4,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 3,8</t>
+          <t>-7,46; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,05</t>
+          <t>-5,55; 8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 13,5</t>
+          <t>-1,13; 13,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,54</t>
+          <t>-4,68; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 6,19</t>
+          <t>-11,39; 6,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 3,88</t>
+          <t>-7,54; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,5</t>
+          <t>4,51; 14,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,16</t>
+          <t>-1,21; 7,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 45,57</t>
+          <t>-3,6; 43,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 5,7</t>
+          <t>-9,95; 5,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 21,39</t>
+          <t>6,15; 21,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,89</t>
+          <t>-1,47; 9,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 210,62</t>
+          <t>-5,77; 200,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,5</t>
+          <t>-0,81; 11,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,77</t>
+          <t>1,74; 14,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,2</t>
+          <t>-1,44; 7,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 9,0</t>
+          <t>-0,13; 9,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 16,56</t>
+          <t>-1,07; 16,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 21,39</t>
+          <t>2,35; 22,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 10,17</t>
+          <t>-1,63; 9,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 13,77</t>
+          <t>-0,21; 14,0</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 7,09</t>
+          <t>-5,7; 6,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 9,89</t>
+          <t>-3,33; 9,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,33</t>
+          <t>4,78; 15,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 5,56</t>
+          <t>-5,07; 5,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 9,47</t>
+          <t>-6,98; 9,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 14,08</t>
+          <t>-4,23; 13,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 20,38</t>
+          <t>5,73; 19,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 8,76</t>
+          <t>-7,25; 8,05</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 7,71</t>
+          <t>-6,33; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,43</t>
+          <t>-5,37; 8,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,53</t>
+          <t>-0,61; 9,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 8,32</t>
+          <t>-1,23; 9,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 10,05</t>
+          <t>-7,41; 10,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,96</t>
+          <t>-6,54; 12,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 11,67</t>
+          <t>-0,66; 11,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 12,0</t>
+          <t>-1,74; 13,2</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,04</t>
+          <t>-0,39; 3,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,72</t>
+          <t>4,09; 8,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,7</t>
+          <t>1,02; 4,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 17,97</t>
+          <t>-1,83; 17,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,87</t>
+          <t>-0,54; 5,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,92</t>
+          <t>5,84; 12,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,86</t>
+          <t>1,22; 6,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 39,57</t>
+          <t>-3,05; 36,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57GLOBAL_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 8,04</t>
+          <t>-4,21; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 11,46</t>
+          <t>-1,56; 10,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 7,34</t>
+          <t>-4,08; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 14,97</t>
+          <t>-6,89; 14,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 13,93</t>
+          <t>-6,61; 13,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 20,0</t>
+          <t>-2,47; 18,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 9,89</t>
+          <t>-5,06; 9,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 38,92</t>
+          <t>-12,73; 34,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,1</t>
+          <t>-7,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-24,1%</t>
+          <t>-11,78%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 6,31</t>
+          <t>-3,67; 6,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 12,83</t>
+          <t>1,75; 12,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,04</t>
+          <t>-5,55; 3,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,25; -4,38</t>
+          <t>-15,1; -0,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 9,56</t>
+          <t>-5,27; 9,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 20,73</t>
+          <t>2,43; 19,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,08</t>
+          <t>-6,6; 4,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,2; -7,84</t>
+          <t>-21,8; -0,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,5%</t>
+          <t>-3,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,92</t>
+          <t>-4,21; 6,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 8,93</t>
+          <t>-1,5; 9,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,43</t>
+          <t>-4,0; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,71</t>
+          <t>-7,44; 3,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 8,84</t>
+          <t>-5,62; 9,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 13,13</t>
+          <t>-2,02; 12,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 5,59</t>
+          <t>-4,74; 5,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 6,29</t>
+          <t>-11,08; 4,98</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,09</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 4,15</t>
+          <t>-7,24; 4,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 14,41</t>
+          <t>4,17; 14,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 7,29</t>
+          <t>-1,74; 6,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 43,61</t>
+          <t>-2,25; 7,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 5,85</t>
+          <t>-9,73; 6,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 21,66</t>
+          <t>5,78; 22,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 9,13</t>
+          <t>-1,93; 8,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 200,48</t>
+          <t>-3,44; 11,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 11,13</t>
+          <t>-0,45; 11,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 14,51</t>
+          <t>1,25; 14,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 7,9</t>
+          <t>-1,66; 7,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,07</t>
+          <t>-0,68; 8,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 16,5</t>
+          <t>-0,54; 16,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 22,7</t>
+          <t>1,75; 22,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 9,81</t>
+          <t>-1,94; 9,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 14,0</t>
+          <t>-0,95; 12,94</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 6,77</t>
+          <t>-5,48; 7,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 9,59</t>
+          <t>-3,72; 9,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,21</t>
+          <t>3,65; 14,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,13</t>
+          <t>-4,69; 5,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 9,23</t>
+          <t>-6,69; 9,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 13,69</t>
+          <t>-4,75; 14,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,73; 19,9</t>
+          <t>4,39; 19,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 8,05</t>
+          <t>-6,73; 8,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 7,88</t>
+          <t>-5,88; 8,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 8,99</t>
+          <t>-5,15; 9,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 9,48</t>
+          <t>-0,92; 9,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 9,11</t>
+          <t>-2,01; 8,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 10,28</t>
+          <t>-6,97; 10,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 12,31</t>
+          <t>-6,26; 12,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 11,63</t>
+          <t>-1,01; 11,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 13,2</t>
+          <t>-2,65; 12,05</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,91</t>
+          <t>-0,48; 4,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,57</t>
+          <t>4,12; 8,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,86</t>
+          <t>1,06; 4,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 17,47</t>
+          <t>-1,33; 3,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,68</t>
+          <t>-0,68; 5,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,8</t>
+          <t>5,89; 12,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,0</t>
+          <t>1,28; 5,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 36,75</t>
+          <t>-2,02; 5,56</t>
         </is>
       </c>
     </row>
